--- a/docs/r01lib_pin_table.xlsx
+++ b/docs/r01lib_pin_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tedd/Desktop/dl/r01/r01lib/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65C43D7-EACB-C34B-8F34-541946C23BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5617F787-E5E9-0445-9275-B0B76A0D21E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="40080" windowHeight="25800" activeTab="5" xr2:uid="{F4A4BD97-1D13-3141-8799-357F4902D58A}"/>
+    <workbookView xWindow="12180" yWindow="780" windowWidth="37640" windowHeight="28760" xr2:uid="{F4A4BD97-1D13-3141-8799-357F4902D58A}"/>
   </bookViews>
   <sheets>
     <sheet name="N947" sheetId="3" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1848" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1880" uniqueCount="416">
   <si>
     <t>FRDM-MCXN947</t>
     <phoneticPr fontId="1"/>
@@ -1471,6 +1471,22 @@
   </si>
   <si>
     <t>FRDM-MCXC444 added</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FRDM-MCXC444 I2C @A4/A5 pin check mark added</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>USBTX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>USBRX</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Serial</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1491,12 +1507,16 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>(Semihost only)</t>
+      <t>(Semihost use only)</t>
     </r>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>FRDM-MCXC444 I2C @A4/A5 pin check mark added</t>
+    <t>Serial class supported pin information added</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FRDM-MCXC444</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1601,7 +1621,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1698,13 +1718,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1753,6 +1782,24 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1761,15 +1808,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1780,22 +1818,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2138,33 +2170,34 @@
     <col min="1" max="16384" width="13.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" s="10" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="14" customHeight="1">
-      <c r="A4" s="16" t="s">
+    <row r="4" spans="1:11" ht="14" customHeight="1">
+      <c r="A4" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="19" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
-      <c r="I4" s="20"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
       <c r="J4" s="21"/>
-    </row>
-    <row r="5" spans="1:10" ht="15">
+      <c r="K4" s="21"/>
+    </row>
+    <row r="5" spans="1:11" ht="15">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -2195,8 +2228,11 @@
       <c r="J5" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5" s="6" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
@@ -2215,8 +2251,9 @@
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -2235,8 +2272,9 @@
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -2255,8 +2293,9 @@
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -2275,8 +2314,9 @@
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="K9" s="3"/>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -2295,8 +2335,9 @@
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
-    </row>
-    <row r="11" spans="1:10">
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
@@ -2315,8 +2356,9 @@
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="K11" s="3"/>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="3" t="s">
         <v>20</v>
       </c>
@@ -2337,8 +2379,9 @@
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="3" t="s">
         <v>22</v>
       </c>
@@ -2357,8 +2400,9 @@
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="K13" s="3"/>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="3" t="s">
         <v>23</v>
       </c>
@@ -2377,8 +2421,9 @@
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="K14" s="3"/>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="3" t="s">
         <v>24</v>
       </c>
@@ -2399,8 +2444,9 @@
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="1:10">
+      <c r="K15" s="3"/>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
@@ -2424,11 +2470,12 @@
       </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
-      <c r="J16" s="22" t="s">
+      <c r="J16" s="25" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="3" t="s">
         <v>28</v>
       </c>
@@ -2450,9 +2497,10 @@
       </c>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="24"/>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="J17" s="27"/>
+      <c r="K17" s="3"/>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="3" t="s">
         <v>30</v>
       </c>
@@ -2474,9 +2522,10 @@
       </c>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
-      <c r="J18" s="24"/>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="J18" s="27"/>
+      <c r="K18" s="3"/>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="3" t="s">
         <v>32</v>
       </c>
@@ -2498,9 +2547,10 @@
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
-      <c r="J19" s="23"/>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="J19" s="26"/>
+      <c r="K19" s="3"/>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="3" t="s">
         <v>34</v>
       </c>
@@ -2518,13 +2568,14 @@
       <c r="G20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H20" s="22" t="s">
+      <c r="H20" s="25" t="s">
         <v>27</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="K20" s="3"/>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="3" t="s">
         <v>36</v>
       </c>
@@ -2542,11 +2593,12 @@
       <c r="G21" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H21" s="23"/>
+      <c r="H21" s="26"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="K21" s="3"/>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
@@ -2559,8 +2611,9 @@
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
-    </row>
-    <row r="23" spans="1:10">
+      <c r="K22" s="3"/>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
@@ -2573,8 +2626,9 @@
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
-    </row>
-    <row r="24" spans="1:10">
+      <c r="K23" s="3"/>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
@@ -2593,8 +2647,9 @@
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
-    </row>
-    <row r="25" spans="1:10">
+      <c r="K24" s="3"/>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="3" t="s">
         <v>41</v>
       </c>
@@ -2613,8 +2668,9 @@
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="K25" s="3"/>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="3" t="s">
         <v>42</v>
       </c>
@@ -2633,8 +2689,9 @@
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
-    </row>
-    <row r="27" spans="1:10">
+      <c r="K26" s="3"/>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="3" t="s">
         <v>43</v>
       </c>
@@ -2655,8 +2712,9 @@
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
-    </row>
-    <row r="28" spans="1:10">
+      <c r="K27" s="3"/>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="3" t="s">
         <v>168</v>
       </c>
@@ -2669,8 +2727,9 @@
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
-    </row>
-    <row r="29" spans="1:10">
+      <c r="K28" s="3"/>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="3" t="s">
         <v>45</v>
       </c>
@@ -2689,8 +2748,9 @@
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
-    </row>
-    <row r="30" spans="1:10">
+      <c r="K29" s="3"/>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="3" t="s">
         <v>46</v>
       </c>
@@ -2709,8 +2769,9 @@
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
-    </row>
-    <row r="31" spans="1:10">
+      <c r="K30" s="3"/>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="3" t="s">
         <v>47</v>
       </c>
@@ -2729,8 +2790,9 @@
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
-    </row>
-    <row r="32" spans="1:10">
+      <c r="K31" s="3"/>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" s="3" t="s">
         <v>49</v>
       </c>
@@ -2749,6 +2811,7 @@
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
+      <c r="K32" s="3"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="3" t="s">
@@ -2769,6 +2832,7 @@
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
+      <c r="K33" s="3"/>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="3" t="s">
@@ -2789,6 +2853,7 @@
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
+      <c r="K34" s="3"/>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="3" t="s">
@@ -2809,6 +2874,7 @@
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
+      <c r="K35" s="3"/>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="3" t="s">
@@ -2829,10 +2895,11 @@
         <v>12</v>
       </c>
       <c r="H36" s="4"/>
-      <c r="I36" s="22" t="s">
+      <c r="I36" s="25" t="s">
         <v>27</v>
       </c>
       <c r="J36" s="4"/>
+      <c r="K36" s="3"/>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="3" t="s">
@@ -2853,8 +2920,9 @@
         <v>12</v>
       </c>
       <c r="H37" s="4"/>
-      <c r="I37" s="23"/>
+      <c r="I37" s="26"/>
       <c r="J37" s="4"/>
+      <c r="K37" s="3"/>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="3" t="s">
@@ -2875,6 +2943,7 @@
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
+      <c r="K38" s="3"/>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="3" t="s">
@@ -2895,6 +2964,7 @@
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
+      <c r="K39" s="3"/>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="3"/>
@@ -2915,51 +2985,88 @@
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
+      <c r="K40" s="3"/>
+    </row>
+    <row r="41" spans="1:14">
+      <c r="A41" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
+      <c r="A42" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="26"/>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="C45" s="25" t="s">
+      <c r="C45" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="D45" s="25"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="25"/>
-      <c r="G45" s="25"/>
-      <c r="H45" s="25"/>
-      <c r="I45" s="25"/>
-      <c r="J45" s="25"/>
-      <c r="K45" s="25"/>
-      <c r="L45" s="25"/>
-      <c r="M45" s="25"/>
-      <c r="N45" s="25"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
+      <c r="G45" s="16"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="16"/>
     </row>
     <row r="46" spans="1:14">
-      <c r="C46" s="25">
+      <c r="C46" s="16">
         <v>0</v>
       </c>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25">
+      <c r="D46" s="16"/>
+      <c r="E46" s="16">
         <v>1</v>
       </c>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25">
+      <c r="F46" s="16"/>
+      <c r="G46" s="16">
         <v>2</v>
       </c>
-      <c r="H46" s="25"/>
-      <c r="I46" s="25">
+      <c r="H46" s="16"/>
+      <c r="I46" s="16">
         <v>3</v>
       </c>
-      <c r="J46" s="25"/>
-      <c r="K46" s="25">
+      <c r="J46" s="16"/>
+      <c r="K46" s="16">
         <v>4</v>
       </c>
-      <c r="L46" s="25"/>
-      <c r="M46" s="25">
+      <c r="L46" s="16"/>
+      <c r="M46" s="16">
         <v>5</v>
       </c>
-      <c r="N46" s="25"/>
+      <c r="N46" s="16"/>
     </row>
     <row r="47" spans="1:14">
       <c r="C47" s="3" t="s">
@@ -3000,7 +3107,7 @@
       </c>
     </row>
     <row r="48" spans="1:14">
-      <c r="A48" s="25" t="s">
+      <c r="A48" s="16" t="s">
         <v>175</v>
       </c>
       <c r="B48" s="3">
@@ -3044,7 +3151,7 @@
       </c>
     </row>
     <row r="49" spans="1:14">
-      <c r="A49" s="25"/>
+      <c r="A49" s="16"/>
       <c r="B49" s="3">
         <f>B48+1</f>
         <v>1</v>
@@ -3087,7 +3194,7 @@
       </c>
     </row>
     <row r="50" spans="1:14">
-      <c r="A50" s="25"/>
+      <c r="A50" s="16"/>
       <c r="B50" s="3">
         <f t="shared" ref="B50:B79" si="0">B49+1</f>
         <v>2</v>
@@ -3130,7 +3237,7 @@
       </c>
     </row>
     <row r="51" spans="1:14">
-      <c r="A51" s="25"/>
+      <c r="A51" s="16"/>
       <c r="B51" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -3173,7 +3280,7 @@
       </c>
     </row>
     <row r="52" spans="1:14">
-      <c r="A52" s="25"/>
+      <c r="A52" s="16"/>
       <c r="B52" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -3216,7 +3323,7 @@
       </c>
     </row>
     <row r="53" spans="1:14">
-      <c r="A53" s="25"/>
+      <c r="A53" s="16"/>
       <c r="B53" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -3259,7 +3366,7 @@
       </c>
     </row>
     <row r="54" spans="1:14">
-      <c r="A54" s="25"/>
+      <c r="A54" s="16"/>
       <c r="B54" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -3302,7 +3409,7 @@
       </c>
     </row>
     <row r="55" spans="1:14">
-      <c r="A55" s="25"/>
+      <c r="A55" s="16"/>
       <c r="B55" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3345,7 +3452,7 @@
       </c>
     </row>
     <row r="56" spans="1:14">
-      <c r="A56" s="25"/>
+      <c r="A56" s="16"/>
       <c r="B56" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3360,7 +3467,7 @@
         <v>137</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>170</v>
+        <v>411</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>274</v>
@@ -3384,7 +3491,7 @@
       </c>
     </row>
     <row r="57" spans="1:14">
-      <c r="A57" s="25"/>
+      <c r="A57" s="16"/>
       <c r="B57" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -3399,7 +3506,7 @@
         <v>138</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>170</v>
+        <v>410</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>275</v>
@@ -3423,7 +3530,7 @@
       </c>
     </row>
     <row r="58" spans="1:14">
-      <c r="A58" s="25"/>
+      <c r="A58" s="16"/>
       <c r="B58" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -3458,7 +3565,7 @@
       <c r="N58" s="9"/>
     </row>
     <row r="59" spans="1:14">
-      <c r="A59" s="25"/>
+      <c r="A59" s="16"/>
       <c r="B59" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -3493,7 +3600,7 @@
       <c r="N59" s="9"/>
     </row>
     <row r="60" spans="1:14">
-      <c r="A60" s="25"/>
+      <c r="A60" s="16"/>
       <c r="B60" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -3528,7 +3635,7 @@
       <c r="N60" s="9"/>
     </row>
     <row r="61" spans="1:14">
-      <c r="A61" s="25"/>
+      <c r="A61" s="16"/>
       <c r="B61" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -3563,7 +3670,7 @@
       <c r="N61" s="9"/>
     </row>
     <row r="62" spans="1:14">
-      <c r="A62" s="25"/>
+      <c r="A62" s="16"/>
       <c r="B62" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -3598,7 +3705,7 @@
       <c r="N62" s="9"/>
     </row>
     <row r="63" spans="1:14">
-      <c r="A63" s="25"/>
+      <c r="A63" s="16"/>
       <c r="B63" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -3633,7 +3740,7 @@
       <c r="N63" s="9"/>
     </row>
     <row r="64" spans="1:14">
-      <c r="A64" s="25"/>
+      <c r="A64" s="16"/>
       <c r="B64" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -3668,7 +3775,7 @@
       <c r="N64" s="9"/>
     </row>
     <row r="65" spans="1:14">
-      <c r="A65" s="25"/>
+      <c r="A65" s="16"/>
       <c r="B65" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -3703,7 +3810,7 @@
       <c r="N65" s="9"/>
     </row>
     <row r="66" spans="1:14">
-      <c r="A66" s="25"/>
+      <c r="A66" s="16"/>
       <c r="B66" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -3738,7 +3845,7 @@
       <c r="N66" s="9"/>
     </row>
     <row r="67" spans="1:14">
-      <c r="A67" s="25"/>
+      <c r="A67" s="16"/>
       <c r="B67" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -3773,7 +3880,7 @@
       <c r="N67" s="9"/>
     </row>
     <row r="68" spans="1:14">
-      <c r="A68" s="25"/>
+      <c r="A68" s="16"/>
       <c r="B68" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -3808,7 +3915,7 @@
       <c r="N68" s="9"/>
     </row>
     <row r="69" spans="1:14">
-      <c r="A69" s="25"/>
+      <c r="A69" s="16"/>
       <c r="B69" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -3843,7 +3950,7 @@
       <c r="N69" s="9"/>
     </row>
     <row r="70" spans="1:14">
-      <c r="A70" s="25"/>
+      <c r="A70" s="16"/>
       <c r="B70" s="3">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -3878,7 +3985,7 @@
       <c r="N70" s="9"/>
     </row>
     <row r="71" spans="1:14">
-      <c r="A71" s="25"/>
+      <c r="A71" s="16"/>
       <c r="B71" s="3">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -3913,7 +4020,7 @@
       <c r="N71" s="9"/>
     </row>
     <row r="72" spans="1:14">
-      <c r="A72" s="25"/>
+      <c r="A72" s="16"/>
       <c r="B72" s="3">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -3936,7 +4043,7 @@
       <c r="N72" s="9"/>
     </row>
     <row r="73" spans="1:14">
-      <c r="A73" s="25"/>
+      <c r="A73" s="16"/>
       <c r="B73" s="3">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -3959,7 +4066,7 @@
       <c r="N73" s="9"/>
     </row>
     <row r="74" spans="1:14">
-      <c r="A74" s="25"/>
+      <c r="A74" s="16"/>
       <c r="B74" s="3">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -3982,7 +4089,7 @@
       <c r="N74" s="9"/>
     </row>
     <row r="75" spans="1:14">
-      <c r="A75" s="25"/>
+      <c r="A75" s="16"/>
       <c r="B75" s="3">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -4005,7 +4112,7 @@
       <c r="N75" s="9"/>
     </row>
     <row r="76" spans="1:14">
-      <c r="A76" s="25"/>
+      <c r="A76" s="16"/>
       <c r="B76" s="3">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -4028,7 +4135,7 @@
       <c r="N76" s="9"/>
     </row>
     <row r="77" spans="1:14">
-      <c r="A77" s="25"/>
+      <c r="A77" s="16"/>
       <c r="B77" s="3">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -4051,7 +4158,7 @@
       <c r="N77" s="9"/>
     </row>
     <row r="78" spans="1:14">
-      <c r="A78" s="25"/>
+      <c r="A78" s="16"/>
       <c r="B78" s="3">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -4078,7 +4185,7 @@
       <c r="N78" s="9"/>
     </row>
     <row r="79" spans="1:14">
-      <c r="A79" s="25"/>
+      <c r="A79" s="16"/>
       <c r="B79" s="3">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -4105,7 +4212,13 @@
       <c r="N79" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
+    <mergeCell ref="K41:K42"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="J16:J19"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="F4:K4"/>
     <mergeCell ref="A48:A79"/>
     <mergeCell ref="C45:N45"/>
     <mergeCell ref="C46:D46"/>
@@ -4114,11 +4227,6 @@
     <mergeCell ref="I46:J46"/>
     <mergeCell ref="K46:L46"/>
     <mergeCell ref="M46:N46"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:J4"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="J16:J19"/>
-    <mergeCell ref="I36:I37"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4128,38 +4236,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CF8339D-3246-D248-B338-467DAA04C626}">
-  <dimension ref="A1:N80"/>
+  <dimension ref="A1:N82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13.7109375" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="16384" width="13.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" s="10" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="26" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="27" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-    </row>
-    <row r="5" spans="1:9" ht="15">
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+    </row>
+    <row r="5" spans="1:10" ht="15">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -4187,8 +4296,11 @@
       <c r="I5" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5" s="6" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
@@ -4208,8 +4320,9 @@
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -4229,8 +4342,9 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -4248,8 +4362,9 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -4267,8 +4382,9 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -4286,8 +4402,9 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
@@ -4305,8 +4422,9 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="3" t="s">
         <v>20</v>
       </c>
@@ -4324,8 +4442,9 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="3" t="s">
         <v>22</v>
       </c>
@@ -4343,8 +4462,9 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="3" t="s">
         <v>23</v>
       </c>
@@ -4362,8 +4482,9 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="3" t="s">
         <v>24</v>
       </c>
@@ -4381,8 +4502,9 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
@@ -4403,11 +4525,12 @@
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="25" t="s">
+      <c r="I16" s="16" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="3" t="s">
         <v>28</v>
       </c>
@@ -4428,9 +4551,10 @@
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="25"/>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="I17" s="16"/>
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="3" t="s">
         <v>30</v>
       </c>
@@ -4451,9 +4575,10 @@
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="25"/>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="I18" s="16"/>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="3" t="s">
         <v>32</v>
       </c>
@@ -4474,9 +4599,10 @@
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="25"/>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="I19" s="16"/>
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="3" t="s">
         <v>34</v>
       </c>
@@ -4496,12 +4622,13 @@
         <v>12</v>
       </c>
       <c r="G20" s="3"/>
-      <c r="H20" s="25" t="s">
+      <c r="H20" s="16" t="s">
         <v>27</v>
       </c>
       <c r="I20" s="3"/>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="J20" s="3"/>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="3" t="s">
         <v>36</v>
       </c>
@@ -4519,10 +4646,11 @@
         <v>12</v>
       </c>
       <c r="G21" s="3"/>
-      <c r="H21" s="25"/>
+      <c r="H21" s="16"/>
       <c r="I21" s="3"/>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
@@ -4540,8 +4668,9 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="J22" s="3"/>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
@@ -4559,8 +4688,9 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="J23" s="3"/>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
@@ -4578,8 +4708,9 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="J24" s="3"/>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="3" t="s">
         <v>41</v>
       </c>
@@ -4599,8 +4730,9 @@
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
-    </row>
-    <row r="26" spans="1:9">
+      <c r="J25" s="3"/>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="3" t="s">
         <v>42</v>
       </c>
@@ -4617,13 +4749,14 @@
       <c r="F26" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="25" t="s">
+      <c r="G26" s="16" t="s">
         <v>27</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="J26" s="3"/>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="3" t="s">
         <v>43</v>
       </c>
@@ -4640,11 +4773,12 @@
       <c r="F27" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="25"/>
+      <c r="G27" s="16"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
-    </row>
-    <row r="28" spans="1:9">
+      <c r="J27" s="3"/>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="3" t="s">
         <v>168</v>
       </c>
@@ -4662,8 +4796,9 @@
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="J28" s="3"/>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="3" t="s">
         <v>45</v>
       </c>
@@ -4681,8 +4816,9 @@
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
-    </row>
-    <row r="30" spans="1:9">
+      <c r="J29" s="3"/>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="3" t="s">
         <v>46</v>
       </c>
@@ -4702,8 +4838,9 @@
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
-    </row>
-    <row r="31" spans="1:9">
+      <c r="J30" s="3"/>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="3" t="s">
         <v>47</v>
       </c>
@@ -4721,8 +4858,9 @@
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
-    </row>
-    <row r="32" spans="1:9">
+      <c r="J31" s="3"/>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="3" t="s">
         <v>49</v>
       </c>
@@ -4740,6 +4878,7 @@
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="3" t="s">
@@ -4759,6 +4898,7 @@
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="3" t="s">
@@ -4780,6 +4920,7 @@
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="3" t="s">
@@ -4799,6 +4940,7 @@
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="3" t="s">
@@ -4820,6 +4962,7 @@
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="3" t="s">
@@ -4841,6 +4984,7 @@
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="3" t="s">
@@ -4857,11 +5001,12 @@
       <c r="F38" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G38" s="25" t="s">
+      <c r="G38" s="16" t="s">
         <v>27</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="3" t="s">
@@ -4878,9 +5023,10 @@
       <c r="F39" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G39" s="25"/>
+      <c r="G39" s="16"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="3"/>
@@ -4900,6 +5046,7 @@
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="3"/>
@@ -4919,6 +5066,7 @@
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="3"/>
@@ -4938,318 +5086,275 @@
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
-    </row>
-    <row r="46" spans="1:14">
-      <c r="A46" s="10" t="s">
+      <c r="J42" s="3"/>
+    </row>
+    <row r="43" spans="1:14">
+      <c r="A43" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
+      <c r="A44" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="26"/>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="C46" s="25" t="s">
+      <c r="C48" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="D46" s="25"/>
-      <c r="E46" s="25"/>
-      <c r="F46" s="25"/>
-      <c r="G46" s="25"/>
-      <c r="H46" s="25"/>
-      <c r="I46" s="25"/>
-      <c r="J46" s="25"/>
-      <c r="K46" s="25"/>
-      <c r="L46" s="25"/>
-      <c r="M46" s="25"/>
-      <c r="N46" s="25"/>
-    </row>
-    <row r="47" spans="1:14">
-      <c r="C47" s="25">
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="16"/>
+      <c r="I48" s="16"/>
+      <c r="J48" s="16"/>
+      <c r="K48" s="16"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
+      <c r="N48" s="16"/>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="C49" s="16">
         <v>0</v>
       </c>
-      <c r="D47" s="25"/>
-      <c r="E47" s="25">
+      <c r="D49" s="16"/>
+      <c r="E49" s="16">
         <v>1</v>
       </c>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25">
+      <c r="F49" s="16"/>
+      <c r="G49" s="16">
         <v>2</v>
       </c>
-      <c r="H47" s="25"/>
-      <c r="I47" s="25">
+      <c r="H49" s="16"/>
+      <c r="I49" s="16">
         <v>3</v>
       </c>
-      <c r="J47" s="25"/>
-      <c r="K47" s="25">
+      <c r="J49" s="16"/>
+      <c r="K49" s="16">
         <v>4</v>
       </c>
-      <c r="L47" s="25"/>
-      <c r="M47" s="25">
+      <c r="L49" s="16"/>
+      <c r="M49" s="16">
         <v>5</v>
       </c>
-      <c r="N47" s="25"/>
-    </row>
-    <row r="48" spans="1:14">
-      <c r="C48" s="3" t="s">
+      <c r="N49" s="16"/>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="C50" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D48" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="E50" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="F48" s="3" t="s">
+      <c r="F50" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="G50" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="H48" s="3" t="s">
+      <c r="H50" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="I48" s="3" t="s">
+      <c r="I50" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="J48" s="3" t="s">
+      <c r="J50" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="K48" s="3" t="s">
+      <c r="K50" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="L48" s="3" t="s">
+      <c r="L50" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="M48" s="3" t="s">
+      <c r="M50" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="N48" s="3" t="s">
+      <c r="N50" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
-      <c r="A49" s="25" t="s">
+    <row r="51" spans="1:14">
+      <c r="A51" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B51" s="3">
         <v>0</v>
       </c>
-      <c r="C49" s="9" t="s">
+      <c r="C51" s="9" t="s">
         <v>176</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14">
-      <c r="A50" s="25"/>
-      <c r="B50" s="3">
-        <f>B49+1</f>
-        <v>1</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="M50" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="N50" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
-      <c r="A51" s="25"/>
-      <c r="B51" s="3">
-        <f t="shared" ref="B51:B80" si="0">B50+1</f>
-        <v>2</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>180</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>170</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>171</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>215</v>
+        <v>69</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>171</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>276</v>
+        <v>127</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>171</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>68</v>
+        <v>102</v>
       </c>
       <c r="L51" s="3" t="s">
         <v>171</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>94</v>
+        <v>286</v>
       </c>
       <c r="N51" s="3" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="52" spans="1:14">
-      <c r="A52" s="25"/>
+      <c r="A52" s="16"/>
       <c r="B52" s="3">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>B51+1</f>
+        <v>1</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>170</v>
       </c>
       <c r="E52" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" s="16"/>
+      <c r="B53" s="3">
+        <f t="shared" ref="B53:B82" si="0">B52+1</f>
+        <v>2</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" s="16"/>
+      <c r="B54" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G52" s="3" t="s">
+      <c r="F54" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G54" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I52" s="9"/>
-      <c r="J52" s="9"/>
-      <c r="K52" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14">
-      <c r="A53" s="25"/>
-      <c r="B53" s="3">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I53" s="9"/>
-      <c r="J53" s="9"/>
-      <c r="K53" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="M53" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="N53" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14">
-      <c r="A54" s="25"/>
-      <c r="B54" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>128</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>171</v>
@@ -5257,188 +5362,204 @@
       <c r="I54" s="9"/>
       <c r="J54" s="9"/>
       <c r="K54" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55" s="16"/>
+      <c r="B55" s="3">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
+      <c r="K55" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="N55" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56" s="16"/>
+      <c r="B56" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
+      <c r="K56" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="M54" s="3" t="s">
+      <c r="L56" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="M56" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14">
-      <c r="A55" s="25"/>
-      <c r="B55" s="3">
+      <c r="N56" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" s="16"/>
+      <c r="B57" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E55" s="3" t="s">
+      <c r="D57" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F55" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G55" s="3" t="s">
+      <c r="F57" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G57" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="H55" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I55" s="3" t="s">
+      <c r="H57" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I57" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="J55" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="K55" s="3" t="s">
+      <c r="J57" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K57" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="L55" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="M55" s="3" t="s">
+      <c r="L57" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="M57" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="N55" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14">
-      <c r="A56" s="25"/>
-      <c r="B56" s="3">
+      <c r="N57" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" s="16"/>
+      <c r="B58" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E56" s="3" t="s">
+      <c r="D58" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="F56" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G56" s="3" t="s">
+      <c r="F58" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G58" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="H56" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I56" s="3" t="s">
+      <c r="H58" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="J56" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="K56" s="3" t="s">
+      <c r="J58" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K58" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="L56" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="M56" s="3" t="s">
+      <c r="L58" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="M58" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="N56" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14">
-      <c r="A57" s="25"/>
-      <c r="B57" s="3">
+      <c r="N58" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" s="16"/>
+      <c r="B59" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
-      </c>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="K57" s="9"/>
-      <c r="L57" s="9"/>
-      <c r="M57" s="9"/>
-      <c r="N57" s="9"/>
-    </row>
-    <row r="58" spans="1:14">
-      <c r="A58" s="25"/>
-      <c r="B58" s="3">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="K58" s="9"/>
-      <c r="L58" s="9"/>
-      <c r="M58" s="9"/>
-      <c r="N58" s="9"/>
-    </row>
-    <row r="59" spans="1:14">
-      <c r="A59" s="25"/>
-      <c r="B59" s="3">
-        <f t="shared" si="0"/>
-        <v>10</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
-      <c r="E59" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>171</v>
+      <c r="E59" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>411</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>155</v>
+        <v>274</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>171</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>171</v>
@@ -5449,27 +5570,27 @@
       <c r="N59" s="9"/>
     </row>
     <row r="60" spans="1:14">
-      <c r="A60" s="25"/>
+      <c r="A60" s="16"/>
       <c r="B60" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
-      <c r="E60" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>171</v>
+      <c r="E60" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="F60" s="9" t="s">
+        <v>410</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>153</v>
+        <v>275</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>171</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>171</v>
@@ -5480,81 +5601,77 @@
       <c r="N60" s="9"/>
     </row>
     <row r="61" spans="1:14">
-      <c r="A61" s="25"/>
+      <c r="A61" s="16"/>
       <c r="B61" s="3">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
+      <c r="G61" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="I61" s="3" t="s">
-        <v>70</v>
+        <v>240</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="K61" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="L61" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="K61" s="9"/>
+      <c r="L61" s="9"/>
       <c r="M61" s="9"/>
       <c r="N61" s="9"/>
     </row>
     <row r="62" spans="1:14">
-      <c r="A62" s="25"/>
+      <c r="A62" s="16"/>
       <c r="B62" s="3">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
       <c r="E62" s="3" t="s">
-        <v>163</v>
+        <v>201</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
-      <c r="I62" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J62" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="G62" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K62" s="9"/>
+      <c r="L62" s="9"/>
       <c r="M62" s="9"/>
       <c r="N62" s="9"/>
     </row>
     <row r="63" spans="1:14">
-      <c r="A63" s="25"/>
+      <c r="A63" s="16"/>
       <c r="B63" s="3">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="C63" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="D63" s="9" t="s">
-        <v>170</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
       <c r="E63" s="3" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>171</v>
@@ -5562,13 +5679,13 @@
       <c r="G63" s="9"/>
       <c r="H63" s="9"/>
       <c r="I63" s="3" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>171</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L63" s="3" t="s">
         <v>171</v>
@@ -5577,33 +5694,29 @@
       <c r="N63" s="9"/>
     </row>
     <row r="64" spans="1:14">
-      <c r="A64" s="25"/>
+      <c r="A64" s="16"/>
       <c r="B64" s="3">
         <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>171</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
       <c r="E64" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G64" s="9"/>
       <c r="H64" s="9"/>
-      <c r="I64" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>171</v>
+      <c r="I64" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="J64" s="9" t="s">
+        <v>170</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="L64" s="3" t="s">
         <v>171</v>
@@ -5612,19 +5725,19 @@
       <c r="N64" s="9"/>
     </row>
     <row r="65" spans="1:14">
-      <c r="A65" s="25"/>
+      <c r="A65" s="16"/>
       <c r="B65" s="3">
         <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>171</v>
+        <v>14</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>170</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>271</v>
+        <v>159</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>171</v>
@@ -5632,13 +5745,13 @@
       <c r="G65" s="9"/>
       <c r="H65" s="9"/>
       <c r="I65" s="3" t="s">
-        <v>158</v>
+        <v>78</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>171</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L65" s="3" t="s">
         <v>171</v>
@@ -5647,33 +5760,33 @@
       <c r="N65" s="9"/>
     </row>
     <row r="66" spans="1:14">
-      <c r="A66" s="25"/>
+      <c r="A66" s="16"/>
       <c r="B66" s="3">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>171</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>86</v>
+        <v>160</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G66" s="9"/>
       <c r="H66" s="9"/>
       <c r="I66" s="3" t="s">
-        <v>74</v>
+        <v>131</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>171</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>171</v>
@@ -5682,19 +5795,19 @@
       <c r="N66" s="9"/>
     </row>
     <row r="67" spans="1:14">
-      <c r="A67" s="25"/>
+      <c r="A67" s="16"/>
       <c r="B67" s="3">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>171</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>171</v>
@@ -5702,13 +5815,13 @@
       <c r="G67" s="9"/>
       <c r="H67" s="9"/>
       <c r="I67" s="3" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>171</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L67" s="3" t="s">
         <v>171</v>
@@ -5717,29 +5830,33 @@
       <c r="N67" s="9"/>
     </row>
     <row r="68" spans="1:14">
-      <c r="A68" s="25"/>
+      <c r="A68" s="16"/>
       <c r="B68" s="3">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>188</v>
+        <v>147</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>171</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>273</v>
+        <v>86</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>171</v>
       </c>
       <c r="G68" s="9"/>
       <c r="H68" s="9"/>
-      <c r="I68" s="9"/>
-      <c r="J68" s="9"/>
+      <c r="I68" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="K68" s="3" t="s">
-        <v>281</v>
+        <v>90</v>
       </c>
       <c r="L68" s="3" t="s">
         <v>171</v>
@@ -5748,29 +5865,33 @@
       <c r="N68" s="9"/>
     </row>
     <row r="69" spans="1:14">
-      <c r="A69" s="25"/>
+      <c r="A69" s="16"/>
       <c r="B69" s="3">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="E69" s="9"/>
-      <c r="F69" s="9"/>
+      <c r="E69" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="G69" s="9"/>
       <c r="H69" s="9"/>
-      <c r="I69" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="J69" s="9" t="s">
-        <v>170</v>
+      <c r="I69" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="J69" s="3" t="s">
+        <v>171</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="L69" s="3" t="s">
         <v>171</v>
@@ -5779,29 +5900,29 @@
       <c r="N69" s="9"/>
     </row>
     <row r="70" spans="1:14">
-      <c r="A70" s="25"/>
+      <c r="A70" s="16"/>
       <c r="B70" s="3">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>72</v>
+        <v>188</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="E70" s="9"/>
-      <c r="F70" s="9"/>
+      <c r="E70" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="G70" s="9"/>
       <c r="H70" s="9"/>
-      <c r="I70" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="J70" s="9" t="s">
-        <v>170</v>
-      </c>
+      <c r="I70" s="9"/>
+      <c r="J70" s="9"/>
       <c r="K70" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="L70" s="3" t="s">
         <v>171</v>
@@ -5810,13 +5931,13 @@
       <c r="N70" s="9"/>
     </row>
     <row r="71" spans="1:14">
-      <c r="A71" s="25"/>
+      <c r="A71" s="16"/>
       <c r="B71" s="3">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>171</v>
@@ -5826,28 +5947,28 @@
       <c r="G71" s="9"/>
       <c r="H71" s="9"/>
       <c r="I71" s="9" t="s">
-        <v>120</v>
+        <v>166</v>
       </c>
       <c r="J71" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="K71" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="L71" s="9" t="s">
-        <v>170</v>
+      <c r="K71" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="L71" s="3" t="s">
+        <v>171</v>
       </c>
       <c r="M71" s="9"/>
       <c r="N71" s="9"/>
     </row>
     <row r="72" spans="1:14">
-      <c r="A72" s="25"/>
+      <c r="A72" s="16"/>
       <c r="B72" s="3">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>171</v>
@@ -5857,13 +5978,13 @@
       <c r="G72" s="9"/>
       <c r="H72" s="9"/>
       <c r="I72" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J72" s="9" t="s">
         <v>170</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>171</v>
@@ -5872,13 +5993,13 @@
       <c r="N72" s="9"/>
     </row>
     <row r="73" spans="1:14">
-      <c r="A73" s="25"/>
+      <c r="A73" s="16"/>
       <c r="B73" s="3">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>171</v>
@@ -5887,21 +6008,29 @@
       <c r="F73" s="9"/>
       <c r="G73" s="9"/>
       <c r="H73" s="9"/>
-      <c r="I73" s="9"/>
-      <c r="J73" s="9"/>
-      <c r="K73" s="9"/>
-      <c r="L73" s="9"/>
+      <c r="I73" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="J73" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="K73" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="L73" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="M73" s="9"/>
       <c r="N73" s="9"/>
     </row>
     <row r="74" spans="1:14">
-      <c r="A74" s="25"/>
+      <c r="A74" s="16"/>
       <c r="B74" s="3">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>268</v>
+        <v>76</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>171</v>
@@ -5910,21 +6039,29 @@
       <c r="F74" s="9"/>
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
-      <c r="I74" s="9"/>
-      <c r="J74" s="9"/>
-      <c r="K74" s="9"/>
-      <c r="L74" s="9"/>
+      <c r="I74" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="J74" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="M74" s="9"/>
       <c r="N74" s="9"/>
     </row>
     <row r="75" spans="1:14">
-      <c r="A75" s="25"/>
+      <c r="A75" s="16"/>
       <c r="B75" s="3">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>269</v>
+        <v>111</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>171</v>
@@ -5941,13 +6078,13 @@
       <c r="N75" s="9"/>
     </row>
     <row r="76" spans="1:14">
-      <c r="A76" s="25"/>
+      <c r="A76" s="16"/>
       <c r="B76" s="3">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>171</v>
@@ -5964,13 +6101,13 @@
       <c r="N76" s="9"/>
     </row>
     <row r="77" spans="1:14">
-      <c r="A77" s="25"/>
+      <c r="A77" s="16"/>
       <c r="B77" s="3">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>108</v>
+        <v>269</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>171</v>
@@ -5987,13 +6124,13 @@
       <c r="N77" s="9"/>
     </row>
     <row r="78" spans="1:14">
-      <c r="A78" s="25"/>
+      <c r="A78" s="16"/>
       <c r="B78" s="3">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>103</v>
+        <v>270</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>171</v>
@@ -6010,19 +6147,19 @@
       <c r="N78" s="9"/>
     </row>
     <row r="79" spans="1:14">
-      <c r="A79" s="25"/>
+      <c r="A79" s="16"/>
       <c r="B79" s="3">
         <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="C79" s="9"/>
-      <c r="D79" s="9"/>
-      <c r="E79" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>170</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9"/>
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="9"/>
@@ -6033,19 +6170,19 @@
       <c r="N79" s="9"/>
     </row>
     <row r="80" spans="1:14">
-      <c r="A80" s="25"/>
+      <c r="A80" s="16"/>
       <c r="B80" s="3">
         <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="C80" s="9"/>
-      <c r="D80" s="9"/>
-      <c r="E80" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="F80" s="9" t="s">
-        <v>170</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9"/>
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="9"/>
@@ -6055,22 +6192,69 @@
       <c r="M80" s="9"/>
       <c r="N80" s="9"/>
     </row>
+    <row r="81" spans="1:14">
+      <c r="A81" s="16"/>
+      <c r="B81" s="3">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C81" s="9"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G81" s="9"/>
+      <c r="H81" s="9"/>
+      <c r="I81" s="9"/>
+      <c r="J81" s="9"/>
+      <c r="K81" s="9"/>
+      <c r="L81" s="9"/>
+      <c r="M81" s="9"/>
+      <c r="N81" s="9"/>
+    </row>
+    <row r="82" spans="1:14">
+      <c r="A82" s="16"/>
+      <c r="B82" s="3">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C82" s="9"/>
+      <c r="D82" s="9"/>
+      <c r="E82" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G82" s="9"/>
+      <c r="H82" s="9"/>
+      <c r="I82" s="9"/>
+      <c r="J82" s="9"/>
+      <c r="K82" s="9"/>
+      <c r="L82" s="9"/>
+      <c r="M82" s="9"/>
+      <c r="N82" s="9"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A49:A80"/>
-    <mergeCell ref="C46:N46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="M47:N47"/>
+  <mergeCells count="15">
+    <mergeCell ref="J43:J44"/>
+    <mergeCell ref="E4:J4"/>
     <mergeCell ref="G26:G27"/>
     <mergeCell ref="H20:H21"/>
     <mergeCell ref="G38:G39"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:I4"/>
     <mergeCell ref="I16:I19"/>
+    <mergeCell ref="A51:A82"/>
+    <mergeCell ref="C48:N48"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="M49:N49"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6079,38 +6263,39 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6DDC342-09CC-8E4E-BCBC-273824CBDD0A}">
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13.7109375" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="16384" width="13.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" s="10" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="26" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="27" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-    </row>
-    <row r="5" spans="1:9" ht="15">
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+    </row>
+    <row r="5" spans="1:10" ht="15">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -6138,8 +6323,11 @@
       <c r="I5" s="7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5" s="6" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
@@ -6157,8 +6345,9 @@
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -6176,8 +6365,9 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -6195,8 +6385,9 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -6216,8 +6407,9 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -6235,8 +6427,9 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
@@ -6254,8 +6447,9 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="3" t="s">
         <v>20</v>
       </c>
@@ -6273,8 +6467,9 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="3" t="s">
         <v>22</v>
       </c>
@@ -6292,8 +6487,9 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="3" t="s">
         <v>23</v>
       </c>
@@ -6311,8 +6507,9 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="3" t="s">
         <v>24</v>
       </c>
@@ -6330,8 +6527,9 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
@@ -6351,8 +6549,9 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>318</v>
@@ -6369,14 +6568,15 @@
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="22" t="s">
+      <c r="I17" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" s="3"/>
+      <c r="K17" s="1" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:11">
       <c r="A18" s="3" t="s">
         <v>28</v>
       </c>
@@ -6393,9 +6593,10 @@
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="24"/>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="I18" s="27"/>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>319</v>
@@ -6412,12 +6613,13 @@
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="1" t="s">
+      <c r="I19" s="27"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="1" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:11">
       <c r="A20" s="3" t="s">
         <v>30</v>
       </c>
@@ -6436,9 +6638,10 @@
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
-      <c r="I20" s="24"/>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="I20" s="27"/>
+      <c r="J20" s="3"/>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="3" t="s">
         <v>32</v>
       </c>
@@ -6457,9 +6660,10 @@
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="23"/>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="I21" s="26"/>
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="3" t="s">
         <v>34</v>
       </c>
@@ -6478,15 +6682,16 @@
       <c r="F22" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G22" s="25" t="s">
+      <c r="G22" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H22" s="25" t="s">
+      <c r="H22" s="16" t="s">
         <v>27</v>
       </c>
       <c r="I22" s="3"/>
-    </row>
-    <row r="23" spans="1:10">
+      <c r="J22" s="3"/>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="3" t="s">
         <v>36</v>
       </c>
@@ -6505,11 +6710,12 @@
       <c r="F23" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
       <c r="I23" s="3"/>
-    </row>
-    <row r="24" spans="1:10">
+      <c r="J23" s="3"/>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="3" t="s">
         <v>38</v>
       </c>
@@ -6527,8 +6733,9 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
-    </row>
-    <row r="25" spans="1:10">
+      <c r="J24" s="3"/>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="3" t="s">
         <v>39</v>
       </c>
@@ -6546,8 +6753,9 @@
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="J25" s="3"/>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="3" t="s">
         <v>40</v>
       </c>
@@ -6565,8 +6773,9 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-    </row>
-    <row r="27" spans="1:10">
+      <c r="J26" s="3"/>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="3" t="s">
         <v>41</v>
       </c>
@@ -6584,8 +6793,9 @@
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
-    </row>
-    <row r="28" spans="1:10">
+      <c r="J27" s="3"/>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="3" t="s">
         <v>42</v>
       </c>
@@ -6603,8 +6813,9 @@
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-    </row>
-    <row r="29" spans="1:10">
+      <c r="J28" s="3"/>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="3" t="s">
         <v>43</v>
       </c>
@@ -6622,8 +6833,9 @@
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
-    </row>
-    <row r="30" spans="1:10">
+      <c r="J29" s="3"/>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="3" t="s">
         <v>168</v>
       </c>
@@ -6641,8 +6853,9 @@
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
-    </row>
-    <row r="31" spans="1:10">
+      <c r="J30" s="3"/>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="3" t="s">
         <v>45</v>
       </c>
@@ -6662,8 +6875,9 @@
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
-    </row>
-    <row r="32" spans="1:10">
+      <c r="J31" s="3"/>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" s="3" t="s">
         <v>46</v>
       </c>
@@ -6682,11 +6896,12 @@
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
-      <c r="I32" s="25" t="s">
+      <c r="I32" s="16" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="33" spans="1:12">
+      <c r="J32" s="3"/>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="3" t="s">
         <v>47</v>
       </c>
@@ -6707,9 +6922,10 @@
         <v>48</v>
       </c>
       <c r="H33" s="3"/>
-      <c r="I33" s="25"/>
-    </row>
-    <row r="34" spans="1:12">
+      <c r="I33" s="16"/>
+      <c r="J33" s="3"/>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="3" t="s">
         <v>49</v>
       </c>
@@ -6728,9 +6944,10 @@
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
-      <c r="I34" s="25"/>
-    </row>
-    <row r="35" spans="1:12">
+      <c r="I34" s="16"/>
+      <c r="J34" s="3"/>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" s="3" t="s">
         <v>50</v>
       </c>
@@ -6751,9 +6968,10 @@
         <v>51</v>
       </c>
       <c r="H35" s="3"/>
-      <c r="I35" s="25"/>
-    </row>
-    <row r="36" spans="1:12">
+      <c r="I35" s="16"/>
+      <c r="J35" s="3"/>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" s="3" t="s">
         <v>52</v>
       </c>
@@ -6771,8 +6989,9 @@
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
-    </row>
-    <row r="37" spans="1:12">
+      <c r="J36" s="3"/>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="3" t="s">
         <v>53</v>
       </c>
@@ -6790,8 +7009,9 @@
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
-    </row>
-    <row r="38" spans="1:12">
+      <c r="J37" s="3"/>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" s="3" t="s">
         <v>54</v>
       </c>
@@ -6809,8 +7029,9 @@
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
-    </row>
-    <row r="39" spans="1:12">
+      <c r="J38" s="3"/>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" s="3" t="s">
         <v>56</v>
       </c>
@@ -6828,8 +7049,9 @@
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
-    </row>
-    <row r="40" spans="1:12">
+      <c r="J39" s="3"/>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" s="3" t="s">
         <v>58</v>
       </c>
@@ -6844,13 +7066,14 @@
       <c r="F40" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G40" s="25" t="s">
+      <c r="G40" s="16" t="s">
         <v>27</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
-    </row>
-    <row r="41" spans="1:12">
+      <c r="J40" s="3"/>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" s="3" t="s">
         <v>59</v>
       </c>
@@ -6865,11 +7088,12 @@
       <c r="F41" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G41" s="25"/>
+      <c r="G41" s="16"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
-    </row>
-    <row r="42" spans="1:12">
+      <c r="J41" s="3"/>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
         <v>44</v>
@@ -6887,8 +7111,9 @@
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
-    </row>
-    <row r="43" spans="1:12">
+      <c r="J42" s="3"/>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
         <v>60</v>
@@ -6906,227 +7131,224 @@
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
-    </row>
-    <row r="47" spans="1:12">
-      <c r="A47" s="10" t="s">
+      <c r="J43" s="3"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="26"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="30"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="31"/>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="31"/>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="C47" s="25" t="s">
+      <c r="C49" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="D47" s="25"/>
-      <c r="E47" s="25"/>
-      <c r="F47" s="25"/>
-      <c r="G47" s="25"/>
-      <c r="H47" s="25"/>
-      <c r="I47" s="25"/>
-      <c r="J47" s="25"/>
-      <c r="K47" s="25"/>
-      <c r="L47" s="25"/>
-    </row>
-    <row r="48" spans="1:12">
-      <c r="C48" s="25">
+      <c r="D49" s="16"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="16"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="16"/>
+      <c r="J49" s="16"/>
+      <c r="K49" s="16"/>
+      <c r="L49" s="16"/>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="C50" s="16">
         <v>0</v>
       </c>
-      <c r="D48" s="25"/>
-      <c r="E48" s="25">
+      <c r="D50" s="16"/>
+      <c r="E50" s="16">
         <v>1</v>
       </c>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25">
+      <c r="F50" s="16"/>
+      <c r="G50" s="16">
         <v>2</v>
       </c>
-      <c r="H48" s="25"/>
-      <c r="I48" s="25">
+      <c r="H50" s="16"/>
+      <c r="I50" s="16">
         <v>3</v>
       </c>
-      <c r="J48" s="25"/>
-      <c r="K48" s="25">
+      <c r="J50" s="16"/>
+      <c r="K50" s="16">
         <v>4</v>
       </c>
-      <c r="L48" s="25"/>
-    </row>
-    <row r="49" spans="1:12">
-      <c r="C49" s="3" t="s">
+      <c r="L50" s="16"/>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="C51" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D51" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E51" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="F51" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="G51" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="H51" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="I49" s="3" t="s">
+      <c r="I51" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="J49" s="3" t="s">
+      <c r="J51" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="K49" s="3" t="s">
+      <c r="K51" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="L49" s="3" t="s">
+      <c r="L51" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
-      <c r="A50" s="25" t="s">
+    <row r="52" spans="1:12">
+      <c r="A52" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B52" s="3">
         <v>0</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="C52" s="9" t="s">
         <v>177</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="K50" s="9"/>
-      <c r="L50" s="9"/>
-    </row>
-    <row r="51" spans="1:12">
-      <c r="A51" s="25"/>
-      <c r="B51" s="3">
-        <f>B50+1</f>
-        <v>1</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="K51" s="9"/>
-      <c r="L51" s="9"/>
-    </row>
-    <row r="52" spans="1:12">
-      <c r="A52" s="25"/>
-      <c r="B52" s="3">
-        <f t="shared" ref="B52:B81" si="0">B51+1</f>
-        <v>2</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>181</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>170</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>171</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="I52" s="9"/>
-      <c r="J52" s="9"/>
-      <c r="K52" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="I52" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K52" s="9"/>
+      <c r="L52" s="9"/>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="25"/>
+      <c r="A53" s="16"/>
       <c r="B53" s="3">
-        <f t="shared" si="0"/>
-        <v>3</v>
+        <f>B52+1</f>
+        <v>1</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>170</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>171</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="I53" s="9"/>
-      <c r="J53" s="9"/>
-      <c r="K53" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="I53" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K53" s="9"/>
+      <c r="L53" s="9"/>
     </row>
     <row r="54" spans="1:12">
-      <c r="A54" s="25"/>
+      <c r="A54" s="16"/>
       <c r="B54" s="3">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
+        <f t="shared" ref="B54:B83" si="0">B53+1</f>
+        <v>2</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>411</v>
+      </c>
       <c r="E54" s="3" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>171</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>126</v>
+        <v>216</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>171</v>
@@ -7134,28 +7356,32 @@
       <c r="I54" s="9"/>
       <c r="J54" s="9"/>
       <c r="K54" s="3" t="s">
-        <v>256</v>
+        <v>99</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" s="25"/>
+      <c r="A55" s="16"/>
       <c r="B55" s="3">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>410</v>
+      </c>
       <c r="E55" s="3" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>171</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>171</v>
@@ -7163,154 +7389,158 @@
       <c r="I55" s="9"/>
       <c r="J55" s="9"/>
       <c r="K55" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="L55" s="3" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="25"/>
+      <c r="A56" s="16"/>
       <c r="B56" s="3">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>171</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
       <c r="E56" s="3" t="s">
-        <v>196</v>
+        <v>124</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>171</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>219</v>
+        <v>126</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="I56" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
       <c r="K56" s="3" t="s">
-        <v>87</v>
+        <v>256</v>
       </c>
       <c r="L56" s="3" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="25"/>
+      <c r="A57" s="16"/>
       <c r="B57" s="3">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
       <c r="E57" s="3" t="s">
-        <v>197</v>
+        <v>125</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>171</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>73</v>
+        <v>218</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
       <c r="K57" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="25"/>
+      <c r="A58" s="16"/>
       <c r="B58" s="3">
         <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
+        <v>6</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="E58" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
+      <c r="G58" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="I58" s="3" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="K58" s="9"/>
-      <c r="L58" s="9"/>
+      <c r="K58" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="25"/>
+      <c r="A59" s="16"/>
       <c r="B59" s="3">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="9"/>
       <c r="E59" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
+      <c r="G59" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="I59" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="K59" s="9"/>
-      <c r="L59" s="9"/>
+      <c r="K59" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="60" spans="1:12">
-      <c r="A60" s="25"/>
+      <c r="A60" s="16"/>
       <c r="B60" s="3">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
       <c r="E60" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
       <c r="I60" s="3" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>171</v>
@@ -7319,27 +7549,23 @@
       <c r="L60" s="9"/>
     </row>
     <row r="61" spans="1:12">
-      <c r="A61" s="25"/>
+      <c r="A61" s="16"/>
       <c r="B61" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
-      <c r="E61" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="E61" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G61" s="9"/>
+      <c r="H61" s="9"/>
       <c r="I61" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>171</v>
@@ -7348,27 +7574,27 @@
       <c r="L61" s="9"/>
     </row>
     <row r="62" spans="1:12">
-      <c r="A62" s="25"/>
+      <c r="A62" s="16"/>
       <c r="B62" s="3">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
       <c r="E62" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>171</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>221</v>
+        <v>156</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>171</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>71</v>
+        <v>241</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>171</v>
@@ -7377,27 +7603,27 @@
       <c r="L62" s="9"/>
     </row>
     <row r="63" spans="1:12">
-      <c r="A63" s="25"/>
+      <c r="A63" s="16"/>
       <c r="B63" s="3">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
-      <c r="E63" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G63" s="9" t="s">
-        <v>222</v>
-      </c>
-      <c r="H63" s="9" t="s">
+      <c r="E63" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="F63" s="9" t="s">
         <v>170</v>
       </c>
+      <c r="G63" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="I63" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>171</v>
@@ -7406,27 +7632,27 @@
       <c r="L63" s="9"/>
     </row>
     <row r="64" spans="1:12">
-      <c r="A64" s="25"/>
+      <c r="A64" s="16"/>
       <c r="B64" s="3">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
       <c r="E64" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>171</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>171</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>132</v>
+        <v>71</v>
       </c>
       <c r="J64" s="3" t="s">
         <v>171</v>
@@ -7435,27 +7661,27 @@
       <c r="L64" s="9"/>
     </row>
     <row r="65" spans="1:12">
-      <c r="A65" s="25"/>
+      <c r="A65" s="16"/>
       <c r="B65" s="3">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
       <c r="E65" s="3" t="s">
-        <v>205</v>
+        <v>141</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G65" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>171</v>
+      <c r="G65" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>170</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>171</v>
@@ -7464,27 +7690,27 @@
       <c r="L65" s="9"/>
     </row>
     <row r="66" spans="1:12">
-      <c r="A66" s="25"/>
+      <c r="A66" s="16"/>
       <c r="B66" s="3">
         <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
+        <v>14</v>
+      </c>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="G66" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>171</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>246</v>
+        <v>132</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>171</v>
@@ -7493,23 +7719,27 @@
       <c r="L66" s="9"/>
     </row>
     <row r="67" spans="1:12">
-      <c r="A67" s="25"/>
+      <c r="A67" s="16"/>
       <c r="B67" s="3">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
-      <c r="H67" s="9"/>
+        <v>15</v>
+      </c>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="I67" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>171</v>
@@ -7518,23 +7748,27 @@
       <c r="L67" s="9"/>
     </row>
     <row r="68" spans="1:12">
-      <c r="A68" s="25"/>
+      <c r="A68" s="16"/>
       <c r="B68" s="3">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>171</v>
       </c>
       <c r="E68" s="9"/>
       <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="9"/>
+      <c r="G68" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="I68" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J68" s="3" t="s">
         <v>171</v>
@@ -7543,27 +7777,23 @@
       <c r="L68" s="9"/>
     </row>
     <row r="69" spans="1:12">
-      <c r="A69" s="25"/>
+      <c r="A69" s="16"/>
       <c r="B69" s="3">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>171</v>
       </c>
       <c r="E69" s="9"/>
       <c r="F69" s="9"/>
-      <c r="G69" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="G69" s="9"/>
+      <c r="H69" s="9"/>
       <c r="I69" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J69" s="3" t="s">
         <v>171</v>
@@ -7572,27 +7802,23 @@
       <c r="L69" s="9"/>
     </row>
     <row r="70" spans="1:12">
-      <c r="A70" s="25"/>
+      <c r="A70" s="16"/>
       <c r="B70" s="3">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>63</v>
+        <v>186</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>171</v>
       </c>
       <c r="E70" s="9"/>
       <c r="F70" s="9"/>
-      <c r="G70" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="G70" s="9"/>
+      <c r="H70" s="9"/>
       <c r="I70" s="3" t="s">
-        <v>121</v>
+        <v>248</v>
       </c>
       <c r="J70" s="3" t="s">
         <v>171</v>
@@ -7601,13 +7827,13 @@
       <c r="L70" s="9"/>
     </row>
     <row r="71" spans="1:12">
-      <c r="A71" s="25"/>
+      <c r="A71" s="16"/>
       <c r="B71" s="3">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>171</v>
@@ -7615,13 +7841,13 @@
       <c r="E71" s="9"/>
       <c r="F71" s="9"/>
       <c r="G71" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>171</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J71" s="3" t="s">
         <v>171</v>
@@ -7630,23 +7856,27 @@
       <c r="L71" s="9"/>
     </row>
     <row r="72" spans="1:12">
-      <c r="A72" s="25"/>
+      <c r="A72" s="16"/>
       <c r="B72" s="3">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>171</v>
       </c>
       <c r="E72" s="9"/>
       <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
-      <c r="H72" s="9"/>
+      <c r="G72" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="I72" s="3" t="s">
-        <v>251</v>
+        <v>121</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>171</v>
@@ -7655,13 +7885,13 @@
       <c r="L72" s="9"/>
     </row>
     <row r="73" spans="1:12">
-      <c r="A73" s="25"/>
+      <c r="A73" s="16"/>
       <c r="B73" s="3">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>171</v>
@@ -7669,55 +7899,75 @@
       <c r="E73" s="9"/>
       <c r="F73" s="9"/>
       <c r="G73" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="I73" s="9"/>
-      <c r="J73" s="9"/>
+      <c r="I73" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="K73" s="9"/>
       <c r="L73" s="9"/>
     </row>
     <row r="74" spans="1:12">
-      <c r="A74" s="25"/>
+      <c r="A74" s="16"/>
       <c r="B74" s="3">
         <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="C74" s="9"/>
-      <c r="D74" s="9"/>
+        <v>22</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="E74" s="9"/>
       <c r="F74" s="9"/>
       <c r="G74" s="9"/>
       <c r="H74" s="9"/>
-      <c r="I74" s="9"/>
-      <c r="J74" s="9"/>
+      <c r="I74" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="K74" s="9"/>
       <c r="L74" s="9"/>
     </row>
     <row r="75" spans="1:12">
-      <c r="A75" s="25"/>
+      <c r="A75" s="16"/>
       <c r="B75" s="3">
         <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="C75" s="9"/>
-      <c r="D75" s="9"/>
+        <v>23</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="E75" s="9"/>
       <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
+      <c r="G75" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="I75" s="9"/>
       <c r="J75" s="9"/>
       <c r="K75" s="9"/>
       <c r="L75" s="9"/>
     </row>
     <row r="76" spans="1:12">
-      <c r="A76" s="25"/>
+      <c r="A76" s="16"/>
       <c r="B76" s="3">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
@@ -7731,10 +7981,10 @@
       <c r="L76" s="9"/>
     </row>
     <row r="77" spans="1:12">
-      <c r="A77" s="25"/>
+      <c r="A77" s="16"/>
       <c r="B77" s="3">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
@@ -7742,20 +7992,16 @@
       <c r="F77" s="9"/>
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
-      <c r="I77" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="I77" s="9"/>
+      <c r="J77" s="9"/>
       <c r="K77" s="9"/>
       <c r="L77" s="9"/>
     </row>
     <row r="78" spans="1:12">
-      <c r="A78" s="25"/>
+      <c r="A78" s="16"/>
       <c r="B78" s="3">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
@@ -7763,33 +8009,25 @@
       <c r="F78" s="9"/>
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
-      <c r="I78" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="J78" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="I78" s="9"/>
+      <c r="J78" s="9"/>
       <c r="K78" s="9"/>
       <c r="L78" s="9"/>
     </row>
     <row r="79" spans="1:12">
-      <c r="A79" s="25"/>
+      <c r="A79" s="16"/>
       <c r="B79" s="3">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
-      <c r="E79" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>170</v>
-      </c>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9"/>
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
       <c r="I79" s="3" t="s">
-        <v>253</v>
+        <v>149</v>
       </c>
       <c r="J79" s="3" t="s">
         <v>171</v>
@@ -7798,23 +8036,19 @@
       <c r="L79" s="9"/>
     </row>
     <row r="80" spans="1:12">
-      <c r="A80" s="25"/>
+      <c r="A80" s="16"/>
       <c r="B80" s="3">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
-      <c r="E80" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="F80" s="9" t="s">
-        <v>170</v>
-      </c>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9"/>
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
       <c r="I80" s="3" t="s">
-        <v>148</v>
+        <v>252</v>
       </c>
       <c r="J80" s="3" t="s">
         <v>171</v>
@@ -7823,15 +8057,15 @@
       <c r="L80" s="9"/>
     </row>
     <row r="81" spans="1:12">
-      <c r="A81" s="25"/>
+      <c r="A81" s="16"/>
       <c r="B81" s="3">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
       <c r="E81" s="9" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>170</v>
@@ -7839,7 +8073,7 @@
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
       <c r="I81" s="3" t="s">
-        <v>142</v>
+        <v>253</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>171</v>
@@ -7847,22 +8081,73 @@
       <c r="K81" s="9"/>
       <c r="L81" s="9"/>
     </row>
+    <row r="82" spans="1:12">
+      <c r="A82" s="16"/>
+      <c r="B82" s="3">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C82" s="9"/>
+      <c r="D82" s="9"/>
+      <c r="E82" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G82" s="9"/>
+      <c r="H82" s="9"/>
+      <c r="I82" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K82" s="9"/>
+      <c r="L82" s="9"/>
+    </row>
+    <row r="83" spans="1:12">
+      <c r="A83" s="16"/>
+      <c r="B83" s="3">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C83" s="9"/>
+      <c r="D83" s="9"/>
+      <c r="E83" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G83" s="9"/>
+      <c r="H83" s="9"/>
+      <c r="I83" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="K83" s="9"/>
+      <c r="L83" s="9"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A50:A81"/>
-    <mergeCell ref="C47:L47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="I48:J48"/>
-    <mergeCell ref="K48:L48"/>
+  <mergeCells count="15">
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="E4:J4"/>
     <mergeCell ref="G40:G41"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:I4"/>
     <mergeCell ref="I32:I35"/>
     <mergeCell ref="G22:G23"/>
     <mergeCell ref="H22:H23"/>
     <mergeCell ref="I17:I21"/>
+    <mergeCell ref="A52:A83"/>
+    <mergeCell ref="C49:L49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="I50:J50"/>
+    <mergeCell ref="K50:L50"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7871,38 +8156,39 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C49DDE-672C-7742-BDA6-D3A8CF011F02}">
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13.7109375" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="16384" width="13.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" s="10" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="26" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="27" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-    </row>
-    <row r="5" spans="1:9" ht="15">
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+    </row>
+    <row r="5" spans="1:10" ht="15">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -7930,8 +8216,11 @@
       <c r="I5" s="7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:9">
+      <c r="J5" s="6" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
@@ -7949,8 +8238,11 @@
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:9">
+      <c r="J6" s="25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
@@ -7968,8 +8260,9 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7" s="26"/>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -7987,8 +8280,9 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -8008,8 +8302,9 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -8029,8 +8324,9 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
@@ -8050,8 +8346,9 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="3" t="s">
         <v>20</v>
       </c>
@@ -8071,8 +8368,9 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="3" t="s">
         <v>22</v>
       </c>
@@ -8092,8 +8390,9 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="3" t="s">
         <v>23</v>
       </c>
@@ -8113,8 +8412,9 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="3" t="s">
         <v>24</v>
       </c>
@@ -8134,8 +8434,9 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
@@ -8156,11 +8457,12 @@
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="25" t="s">
+      <c r="I16" s="16" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="3" t="s">
         <v>28</v>
       </c>
@@ -8181,9 +8483,10 @@
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="25"/>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="I17" s="16"/>
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="3" t="s">
         <v>30</v>
       </c>
@@ -8204,9 +8507,10 @@
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="25"/>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="I18" s="16"/>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="3" t="s">
         <v>32</v>
       </c>
@@ -8227,9 +8531,10 @@
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="25"/>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="I19" s="16"/>
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="3" t="s">
         <v>34</v>
       </c>
@@ -8246,15 +8551,16 @@
       <c r="F20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="25" t="s">
+      <c r="G20" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="H20" s="25" t="s">
+      <c r="H20" s="16" t="s">
         <v>27</v>
       </c>
       <c r="I20" s="3"/>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="J20" s="3"/>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="3" t="s">
         <v>36</v>
       </c>
@@ -8271,11 +8577,12 @@
       <c r="F21" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
       <c r="I21" s="3"/>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
@@ -8293,8 +8600,9 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="J22" s="3"/>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
@@ -8312,8 +8620,9 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="J23" s="3"/>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
@@ -8331,8 +8640,9 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="J24" s="3"/>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="3" t="s">
         <v>41</v>
       </c>
@@ -8350,8 +8660,9 @@
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
-    </row>
-    <row r="26" spans="1:9">
+      <c r="J25" s="3"/>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="3" t="s">
         <v>42</v>
       </c>
@@ -8369,8 +8680,9 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="J26" s="3"/>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="3" t="s">
         <v>43</v>
       </c>
@@ -8390,8 +8702,9 @@
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
-    </row>
-    <row r="28" spans="1:9">
+      <c r="J27" s="3"/>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="3" t="s">
         <v>168</v>
       </c>
@@ -8411,8 +8724,9 @@
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="J28" s="3"/>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="3" t="s">
         <v>45</v>
       </c>
@@ -8432,8 +8746,9 @@
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
-    </row>
-    <row r="30" spans="1:9">
+      <c r="J29" s="3"/>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="3" t="s">
         <v>46</v>
       </c>
@@ -8451,8 +8766,9 @@
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
-    </row>
-    <row r="31" spans="1:9">
+      <c r="J30" s="3"/>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="3" t="s">
         <v>47</v>
       </c>
@@ -8472,8 +8788,9 @@
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
-    </row>
-    <row r="32" spans="1:9">
+      <c r="J31" s="3"/>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="3" t="s">
         <v>49</v>
       </c>
@@ -8491,6 +8808,7 @@
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="3" t="s">
@@ -8512,6 +8830,7 @@
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="3" t="s">
@@ -8531,6 +8850,7 @@
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="3" t="s">
@@ -8552,6 +8872,7 @@
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="3" t="s">
@@ -8573,6 +8894,9 @@
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
+      <c r="J36" s="25" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="3" t="s">
@@ -8594,6 +8918,7 @@
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
+      <c r="J37" s="26"/>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="3" t="s">
@@ -8610,11 +8935,12 @@
       <c r="F38" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G38" s="25" t="s">
+      <c r="G38" s="16" t="s">
         <v>27</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="3" t="s">
@@ -8631,9 +8957,10 @@
       <c r="F39" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G39" s="25"/>
+      <c r="G39" s="16"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="3"/>
@@ -8651,10 +8978,11 @@
         <v>12</v>
       </c>
       <c r="G40" s="3"/>
-      <c r="H40" s="25" t="s">
+      <c r="H40" s="16" t="s">
         <v>27</v>
       </c>
       <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="3"/>
@@ -8672,8 +9000,9 @@
         <v>12</v>
       </c>
       <c r="G41" s="3"/>
-      <c r="H41" s="25"/>
+      <c r="H41" s="16"/>
       <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="3"/>
@@ -8693,6 +9022,7 @@
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="3"/>
@@ -8712,222 +9042,193 @@
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="26"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="J46" s="31"/>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="10" t="s">
+      <c r="J47" s="31"/>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="J48" s="31"/>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="C47" s="28" t="s">
+      <c r="C50" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="29"/>
-      <c r="I47" s="29"/>
-      <c r="J47" s="30"/>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="C48" s="25">
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="18"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="19"/>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="C51" s="16">
         <v>0</v>
       </c>
-      <c r="D48" s="25"/>
-      <c r="E48" s="25">
+      <c r="D51" s="16"/>
+      <c r="E51" s="16">
         <v>1</v>
       </c>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25">
+      <c r="F51" s="16"/>
+      <c r="G51" s="16">
         <v>2</v>
       </c>
-      <c r="H48" s="25"/>
-      <c r="I48" s="25">
+      <c r="H51" s="16"/>
+      <c r="I51" s="16">
         <v>3</v>
       </c>
-      <c r="J48" s="25"/>
-    </row>
-    <row r="49" spans="1:10">
-      <c r="C49" s="3" t="s">
+      <c r="J51" s="16"/>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="C52" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="D52" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E52" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="F52" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="G52" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="H52" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="I49" s="3" t="s">
+      <c r="I52" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="J49" s="3" t="s">
+      <c r="J52" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
-      <c r="A50" s="25" t="s">
+    <row r="53" spans="1:10">
+      <c r="A53" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B53" s="3">
         <v>0</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="C53" s="9" t="s">
         <v>176</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51" s="25"/>
-      <c r="B51" s="3">
-        <f>B50+1</f>
-        <v>1</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
-      <c r="A52" s="25"/>
-      <c r="B52" s="3">
-        <f t="shared" ref="B52:B81" si="0">B51+1</f>
-        <v>2</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I52" s="9"/>
-      <c r="J52" s="9"/>
-    </row>
-    <row r="53" spans="1:10">
-      <c r="A53" s="25"/>
-      <c r="B53" s="3">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>182</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>170</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>171</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>161</v>
+        <v>69</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="I53" s="9"/>
-      <c r="J53" s="9"/>
+      <c r="I53" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="25"/>
+      <c r="A54" s="16"/>
       <c r="B54" s="3">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
+        <f>B53+1</f>
+        <v>1</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="E54" s="3" t="s">
-        <v>193</v>
+        <v>84</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>171</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>162</v>
+        <v>213</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9"/>
+      <c r="I54" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="25"/>
+      <c r="A55" s="16"/>
       <c r="B55" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
+        <f t="shared" ref="B55:B84" si="0">B54+1</f>
+        <v>2</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>411</v>
+      </c>
       <c r="E55" s="3" t="s">
-        <v>194</v>
+        <v>83</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>171</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>128</v>
+        <v>215</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>171</v>
@@ -8936,294 +9237,306 @@
       <c r="J55" s="9"/>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="25"/>
+      <c r="A56" s="16"/>
       <c r="B56" s="3">
         <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>171</v>
+        <v>3</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>410</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>195</v>
+        <v>79</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>171</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="I56" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="25"/>
+      <c r="A57" s="16"/>
       <c r="B57" s="3">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
       <c r="E57" s="3" t="s">
-        <v>145</v>
+        <v>193</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G57" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="I57" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="J57" s="9" t="s">
-        <v>170</v>
-      </c>
+      <c r="G57" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="25"/>
+      <c r="A58" s="16"/>
       <c r="B58" s="3">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
       <c r="E58" s="3" t="s">
-        <v>137</v>
+        <v>194</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
-      <c r="I58" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="J58" s="9" t="s">
-        <v>170</v>
-      </c>
+      <c r="G58" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="25"/>
+      <c r="A59" s="16"/>
       <c r="B59" s="3">
         <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
+        <v>6</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="E59" s="3" t="s">
-        <v>138</v>
+        <v>195</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G59" s="9"/>
-      <c r="H59" s="9"/>
-      <c r="I59" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="J59" s="9" t="s">
-        <v>170</v>
+      <c r="G59" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="25"/>
+      <c r="A60" s="16"/>
       <c r="B60" s="3">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="9"/>
       <c r="E60" s="3" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G60" s="9"/>
-      <c r="H60" s="9"/>
+      <c r="G60" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="I60" s="9" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="J60" s="9" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="25"/>
+      <c r="A61" s="16"/>
       <c r="B61" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
-      <c r="E61" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="F61" s="9" t="s">
-        <v>170</v>
+      <c r="E61" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>171</v>
       </c>
       <c r="G61" s="9"/>
       <c r="H61" s="9"/>
       <c r="I61" s="9" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="J61" s="9" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="25"/>
+      <c r="A62" s="16"/>
       <c r="B62" s="3">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
       <c r="E62" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>171</v>
+      <c r="G62" s="9"/>
+      <c r="H62" s="9"/>
+      <c r="I62" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="J62" s="9" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="25"/>
+      <c r="A63" s="16"/>
       <c r="B63" s="3">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
       <c r="E63" s="3" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="G63" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>171</v>
+      <c r="G63" s="9"/>
+      <c r="H63" s="9"/>
+      <c r="I63" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="J63" s="9" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="25"/>
+      <c r="A64" s="16"/>
       <c r="B64" s="3">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
-      <c r="E64" s="9"/>
-      <c r="F64" s="9"/>
+      <c r="E64" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="G64" s="9"/>
       <c r="H64" s="9"/>
-      <c r="I64" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>171</v>
+      <c r="I64" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="J64" s="9" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="25"/>
+      <c r="A65" s="16"/>
       <c r="B65" s="3">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
+      <c r="E65" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="I65" s="3" t="s">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="25"/>
+      <c r="A66" s="16"/>
       <c r="B66" s="3">
         <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="E66" s="9"/>
-      <c r="F66" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="G66" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="I66" s="9"/>
-      <c r="J66" s="9"/>
+      <c r="I66" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="25"/>
+      <c r="A67" s="16"/>
       <c r="B67" s="3">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>171</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
       <c r="E67" s="9"/>
       <c r="F67" s="9"/>
       <c r="G67" s="9"/>
       <c r="H67" s="9"/>
-      <c r="I67" s="9"/>
-      <c r="J67" s="9"/>
+      <c r="I67" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="25"/>
+      <c r="A68" s="16"/>
       <c r="B68" s="3">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
@@ -9231,32 +9544,48 @@
       <c r="F68" s="9"/>
       <c r="G68" s="9"/>
       <c r="H68" s="9"/>
-      <c r="I68" s="9"/>
-      <c r="J68" s="9"/>
+      <c r="I68" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J68" s="3" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="25"/>
+      <c r="A69" s="16"/>
       <c r="B69" s="3">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="C69" s="9"/>
-      <c r="D69" s="9"/>
+        <v>16</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="E69" s="9"/>
       <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
-      <c r="H69" s="9"/>
+      <c r="G69" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="I69" s="9"/>
       <c r="J69" s="9"/>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="25"/>
+      <c r="A70" s="16"/>
       <c r="B70" s="3">
         <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="C70" s="9"/>
-      <c r="D70" s="9"/>
+        <v>17</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="E70" s="9"/>
       <c r="F70" s="9"/>
       <c r="G70" s="9"/>
@@ -9265,10 +9594,10 @@
       <c r="J70" s="9"/>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="25"/>
+      <c r="A71" s="16"/>
       <c r="B71" s="3">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
@@ -9280,10 +9609,10 @@
       <c r="J71" s="9"/>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="25"/>
+      <c r="A72" s="16"/>
       <c r="B72" s="3">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
@@ -9295,10 +9624,10 @@
       <c r="J72" s="9"/>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="25"/>
+      <c r="A73" s="16"/>
       <c r="B73" s="3">
         <f t="shared" si="0"/>
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="9"/>
@@ -9310,10 +9639,10 @@
       <c r="J73" s="9"/>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="25"/>
+      <c r="A74" s="16"/>
       <c r="B74" s="3">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
@@ -9325,10 +9654,10 @@
       <c r="J74" s="9"/>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="25"/>
+      <c r="A75" s="16"/>
       <c r="B75" s="3">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
@@ -9340,10 +9669,10 @@
       <c r="J75" s="9"/>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="25"/>
+      <c r="A76" s="16"/>
       <c r="B76" s="3">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
@@ -9355,10 +9684,10 @@
       <c r="J76" s="9"/>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="25"/>
+      <c r="A77" s="16"/>
       <c r="B77" s="3">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
@@ -9366,18 +9695,14 @@
       <c r="F77" s="9"/>
       <c r="G77" s="9"/>
       <c r="H77" s="9"/>
-      <c r="I77" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="J77" s="9" t="s">
-        <v>170</v>
-      </c>
+      <c r="I77" s="9"/>
+      <c r="J77" s="9"/>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="25"/>
+      <c r="A78" s="16"/>
       <c r="B78" s="3">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
@@ -9385,97 +9710,149 @@
       <c r="F78" s="9"/>
       <c r="G78" s="9"/>
       <c r="H78" s="9"/>
-      <c r="I78" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="J78" s="9" t="s">
-        <v>170</v>
-      </c>
+      <c r="I78" s="9"/>
+      <c r="J78" s="9"/>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="25"/>
+      <c r="A79" s="16"/>
       <c r="B79" s="3">
         <f t="shared" si="0"/>
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
-      <c r="E79" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>170</v>
-      </c>
+      <c r="E79" s="9"/>
+      <c r="F79" s="9"/>
       <c r="G79" s="9"/>
       <c r="H79" s="9"/>
-      <c r="I79" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="J79" s="3" t="s">
-        <v>171</v>
-      </c>
+      <c r="I79" s="9"/>
+      <c r="J79" s="9"/>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="25"/>
+      <c r="A80" s="16"/>
       <c r="B80" s="3">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
-      <c r="E80" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="F80" s="9" t="s">
-        <v>170</v>
-      </c>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9"/>
       <c r="G80" s="9"/>
       <c r="H80" s="9"/>
-      <c r="I80" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="J80" s="3" t="s">
-        <v>171</v>
+      <c r="I80" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="J80" s="9" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="81" spans="1:10">
-      <c r="A81" s="25"/>
+      <c r="A81" s="16"/>
       <c r="B81" s="3">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
-      <c r="E81" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>170</v>
-      </c>
+      <c r="E81" s="9"/>
+      <c r="F81" s="9"/>
       <c r="G81" s="9"/>
       <c r="H81" s="9"/>
-      <c r="I81" s="3" t="s">
+      <c r="I81" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="J81" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82" s="16"/>
+      <c r="B82" s="3">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C82" s="9"/>
+      <c r="D82" s="9"/>
+      <c r="E82" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G82" s="9"/>
+      <c r="H82" s="9"/>
+      <c r="I82" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83" s="16"/>
+      <c r="B83" s="3">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C83" s="9"/>
+      <c r="D83" s="9"/>
+      <c r="E83" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="F83" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G83" s="9"/>
+      <c r="H83" s="9"/>
+      <c r="I83" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84" s="16"/>
+      <c r="B84" s="3">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C84" s="9"/>
+      <c r="D84" s="9"/>
+      <c r="E84" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="G84" s="9"/>
+      <c r="H84" s="9"/>
+      <c r="I84" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="J81" s="3" t="s">
+      <c r="J84" s="3" t="s">
         <v>171</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A50:A81"/>
-    <mergeCell ref="C47:J47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="I48:J48"/>
+  <mergeCells count="16">
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="J6:J7"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="H40:H41"/>
     <mergeCell ref="G38:G39"/>
-    <mergeCell ref="E4:I4"/>
     <mergeCell ref="I16:I19"/>
     <mergeCell ref="G20:G21"/>
     <mergeCell ref="H20:H21"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="A53:A84"/>
+    <mergeCell ref="C50:J50"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="I51:J51"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9487,35 +9864,38 @@
   <dimension ref="A1:L81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13.7109375" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="16384" width="13.7109375" style="1"/>
+    <col min="1" max="4" width="13.7109375" style="1"/>
+    <col min="5" max="6" width="15.28515625" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="13.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="10" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="26" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="27" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-    </row>
-    <row r="5" spans="1:9" ht="15">
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+    </row>
+    <row r="5" spans="1:10" ht="15">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -9543,46 +9923,57 @@
       <c r="I5" s="7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="38">
+      <c r="J5" s="6" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="38">
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="3"/>
+      <c r="B6" s="3" t="s">
+        <v>411</v>
+      </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3" t="s">
         <v>328</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:9" ht="38">
+      <c r="J6" s="25" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="38">
       <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="3"/>
+      <c r="B7" s="3" t="s">
+        <v>410</v>
+      </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3" t="s">
         <v>330</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9">
+      <c r="J7" s="26"/>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -9602,8 +9993,9 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
@@ -9623,8 +10015,9 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
@@ -9644,8 +10037,9 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
@@ -9662,8 +10056,9 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="3" t="s">
         <v>20</v>
       </c>
@@ -9683,8 +10078,9 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="3" t="s">
         <v>22</v>
       </c>
@@ -9704,8 +10100,9 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="3" t="s">
         <v>23</v>
       </c>
@@ -9723,8 +10120,9 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="3" t="s">
         <v>24</v>
       </c>
@@ -9742,8 +10140,9 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="3" t="s">
         <v>25</v>
       </c>
@@ -9762,11 +10161,12 @@
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="25" t="s">
+      <c r="I16" s="16" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="3" t="s">
         <v>28</v>
       </c>
@@ -9785,9 +10185,10 @@
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
-      <c r="I17" s="25"/>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="I17" s="16"/>
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="3" t="s">
         <v>30</v>
       </c>
@@ -9806,9 +10207,10 @@
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-      <c r="I18" s="25"/>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="I18" s="16"/>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="3" t="s">
         <v>32</v>
       </c>
@@ -9829,9 +10231,10 @@
       </c>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-      <c r="I19" s="25"/>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="I19" s="16"/>
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="3" t="s">
         <v>34</v>
       </c>
@@ -9850,13 +10253,14 @@
       <c r="F20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="25" t="s">
+      <c r="G20" s="16" t="s">
         <v>27</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="J20" s="3"/>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="3" t="s">
         <v>36</v>
       </c>
@@ -9875,11 +10279,12 @@
       <c r="F21" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="25"/>
+      <c r="G21" s="16"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
@@ -9899,8 +10304,9 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="J22" s="3"/>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
@@ -9918,8 +10324,9 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="J23" s="3"/>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
@@ -9937,8 +10344,9 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="J24" s="3"/>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" s="3" t="s">
         <v>41</v>
       </c>
@@ -9956,8 +10364,9 @@
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
-    </row>
-    <row r="26" spans="1:9">
+      <c r="J25" s="3"/>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" s="3" t="s">
         <v>42</v>
       </c>
@@ -9974,13 +10383,14 @@
       <c r="F26" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="25" t="s">
+      <c r="G26" s="16" t="s">
         <v>27</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="J26" s="3"/>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" s="3" t="s">
         <v>43</v>
       </c>
@@ -9997,11 +10407,12 @@
       <c r="F27" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="25"/>
+      <c r="G27" s="16"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
-    </row>
-    <row r="28" spans="1:9">
+      <c r="J27" s="3"/>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" s="3" t="s">
         <v>168</v>
       </c>
@@ -10021,8 +10432,9 @@
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-    </row>
-    <row r="29" spans="1:9">
+      <c r="J28" s="3"/>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" s="3" t="s">
         <v>45</v>
       </c>
@@ -10042,8 +10454,9 @@
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
-    </row>
-    <row r="30" spans="1:9">
+      <c r="J29" s="3"/>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" s="3" t="s">
         <v>46</v>
       </c>
@@ -10064,11 +10477,12 @@
       </c>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
-      <c r="I30" s="25" t="s">
+      <c r="I30" s="16" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="31" spans="1:9">
+      <c r="J30" s="3"/>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" s="3" t="s">
         <v>47</v>
       </c>
@@ -10089,9 +10503,10 @@
       </c>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
-      <c r="I31" s="25"/>
-    </row>
-    <row r="32" spans="1:9">
+      <c r="I31" s="16"/>
+      <c r="J31" s="3"/>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" s="3" t="s">
         <v>49</v>
       </c>
@@ -10112,7 +10527,8 @@
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
-      <c r="I32" s="25"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="3"/>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="3" t="s">
@@ -10135,7 +10551,8 @@
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
-      <c r="I33" s="25"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="3"/>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="3" t="s">
@@ -10157,6 +10574,7 @@
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="3" t="s">
@@ -10178,6 +10596,7 @@
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="3" t="s">
@@ -10198,11 +10617,14 @@
       <c r="F36" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G36" s="25" t="s">
+      <c r="G36" s="16" t="s">
         <v>27</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
+      <c r="J36" s="25" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="3" t="s">
@@ -10223,9 +10645,10 @@
       <c r="F37" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G37" s="25"/>
+      <c r="G37" s="16"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
+      <c r="J37" s="26"/>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="3" t="s">
@@ -10244,11 +10667,12 @@
       <c r="F38" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G38" s="25" t="s">
+      <c r="G38" s="16" t="s">
         <v>27</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="3" t="s">
@@ -10267,9 +10691,10 @@
       <c r="F39" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="G39" s="25"/>
+      <c r="G39" s="16"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="3"/>
@@ -10289,6 +10714,7 @@
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="3"/>
@@ -10304,6 +10730,7 @@
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="3" t="s">
@@ -10323,6 +10750,7 @@
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" s="3" t="s">
@@ -10344,45 +10772,46 @@
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="C47" s="28" t="s">
+      <c r="C47" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="29"/>
-      <c r="I47" s="29"/>
-      <c r="J47" s="30"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="18"/>
+      <c r="I47" s="18"/>
+      <c r="J47" s="19"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
     </row>
     <row r="48" spans="1:12">
-      <c r="C48" s="25" t="s">
+      <c r="C48" s="16" t="s">
         <v>371</v>
       </c>
-      <c r="D48" s="25"/>
-      <c r="E48" s="25" t="s">
+      <c r="D48" s="16"/>
+      <c r="E48" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="F48" s="25"/>
-      <c r="G48" s="25" t="s">
+      <c r="F48" s="16"/>
+      <c r="G48" s="16" t="s">
         <v>373</v>
       </c>
-      <c r="H48" s="25"/>
-      <c r="I48" s="25" t="s">
+      <c r="H48" s="16"/>
+      <c r="I48" s="16" t="s">
         <v>374</v>
       </c>
-      <c r="J48" s="25"/>
-      <c r="K48" s="25" t="s">
+      <c r="J48" s="16"/>
+      <c r="K48" s="16" t="s">
         <v>375</v>
       </c>
-      <c r="L48" s="25"/>
+      <c r="L48" s="16"/>
     </row>
     <row r="49" spans="1:12">
       <c r="C49" s="3" t="s">
@@ -10417,7 +10846,7 @@
       </c>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="25" t="s">
+      <c r="A50" s="16" t="s">
         <v>175</v>
       </c>
       <c r="B50" s="3">
@@ -10455,7 +10884,7 @@
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="25"/>
+      <c r="A51" s="16"/>
       <c r="B51" s="3">
         <f>B50+1</f>
         <v>1</v>
@@ -10492,7 +10921,7 @@
       </c>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="25"/>
+      <c r="A52" s="16"/>
       <c r="B52" s="3">
         <f t="shared" ref="B52:B81" si="0">B51+1</f>
         <v>2</v>
@@ -10525,7 +10954,7 @@
       <c r="L52" s="9"/>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="25"/>
+      <c r="A53" s="16"/>
       <c r="B53" s="3">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -10558,7 +10987,7 @@
       <c r="L53" s="9"/>
     </row>
     <row r="54" spans="1:12">
-      <c r="A54" s="25"/>
+      <c r="A54" s="16"/>
       <c r="B54" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -10587,7 +11016,7 @@
       <c r="L54" s="9"/>
     </row>
     <row r="55" spans="1:12">
-      <c r="A55" s="25"/>
+      <c r="A55" s="16"/>
       <c r="B55" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -10616,7 +11045,7 @@
       <c r="L55" s="9"/>
     </row>
     <row r="56" spans="1:12">
-      <c r="A56" s="25"/>
+      <c r="A56" s="16"/>
       <c r="B56" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -10641,7 +11070,7 @@
       <c r="L56" s="9"/>
     </row>
     <row r="57" spans="1:12">
-      <c r="A57" s="25"/>
+      <c r="A57" s="16"/>
       <c r="B57" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -10666,7 +11095,7 @@
       <c r="L57" s="9"/>
     </row>
     <row r="58" spans="1:12">
-      <c r="A58" s="25"/>
+      <c r="A58" s="16"/>
       <c r="B58" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -10683,7 +11112,7 @@
       <c r="L58" s="9"/>
     </row>
     <row r="59" spans="1:12">
-      <c r="A59" s="25"/>
+      <c r="A59" s="16"/>
       <c r="B59" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -10700,7 +11129,7 @@
       <c r="L59" s="9"/>
     </row>
     <row r="60" spans="1:12">
-      <c r="A60" s="25"/>
+      <c r="A60" s="16"/>
       <c r="B60" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -10717,7 +11146,7 @@
       <c r="L60" s="9"/>
     </row>
     <row r="61" spans="1:12">
-      <c r="A61" s="25"/>
+      <c r="A61" s="16"/>
       <c r="B61" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -10734,7 +11163,7 @@
       <c r="L61" s="9"/>
     </row>
     <row r="62" spans="1:12">
-      <c r="A62" s="25"/>
+      <c r="A62" s="16"/>
       <c r="B62" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -10755,7 +11184,7 @@
       <c r="L62" s="9"/>
     </row>
     <row r="63" spans="1:12">
-      <c r="A63" s="25"/>
+      <c r="A63" s="16"/>
       <c r="B63" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -10776,7 +11205,7 @@
       <c r="L63" s="9"/>
     </row>
     <row r="64" spans="1:12">
-      <c r="A64" s="25"/>
+      <c r="A64" s="16"/>
       <c r="B64" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -10793,7 +11222,7 @@
       <c r="L64" s="9"/>
     </row>
     <row r="65" spans="1:12">
-      <c r="A65" s="25"/>
+      <c r="A65" s="16"/>
       <c r="B65" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -10810,7 +11239,7 @@
       <c r="L65" s="9"/>
     </row>
     <row r="66" spans="1:12">
-      <c r="A66" s="25"/>
+      <c r="A66" s="16"/>
       <c r="B66" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -10831,7 +11260,7 @@
       <c r="L66" s="9"/>
     </row>
     <row r="67" spans="1:12">
-      <c r="A67" s="25"/>
+      <c r="A67" s="16"/>
       <c r="B67" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -10852,7 +11281,7 @@
       <c r="L67" s="9"/>
     </row>
     <row r="68" spans="1:12">
-      <c r="A68" s="25"/>
+      <c r="A68" s="16"/>
       <c r="B68" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -10877,7 +11306,7 @@
       <c r="L68" s="9"/>
     </row>
     <row r="69" spans="1:12">
-      <c r="A69" s="25"/>
+      <c r="A69" s="16"/>
       <c r="B69" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -10902,7 +11331,7 @@
       <c r="L69" s="9"/>
     </row>
     <row r="70" spans="1:12">
-      <c r="A70" s="25"/>
+      <c r="A70" s="16"/>
       <c r="B70" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -10931,7 +11360,7 @@
       </c>
     </row>
     <row r="71" spans="1:12">
-      <c r="A71" s="25"/>
+      <c r="A71" s="16"/>
       <c r="B71" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -10956,7 +11385,7 @@
       </c>
     </row>
     <row r="72" spans="1:12">
-      <c r="A72" s="25"/>
+      <c r="A72" s="16"/>
       <c r="B72" s="3">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -10981,7 +11410,7 @@
       </c>
     </row>
     <row r="73" spans="1:12">
-      <c r="A73" s="25"/>
+      <c r="A73" s="16"/>
       <c r="B73" s="3">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -11006,7 +11435,7 @@
       </c>
     </row>
     <row r="74" spans="1:12">
-      <c r="A74" s="25"/>
+      <c r="A74" s="16"/>
       <c r="B74" s="3">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -11027,7 +11456,7 @@
       </c>
     </row>
     <row r="75" spans="1:12">
-      <c r="A75" s="25"/>
+      <c r="A75" s="16"/>
       <c r="B75" s="3">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -11048,7 +11477,7 @@
       </c>
     </row>
     <row r="76" spans="1:12">
-      <c r="A76" s="25"/>
+      <c r="A76" s="16"/>
       <c r="B76" s="3">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -11065,7 +11494,7 @@
       <c r="L76" s="9"/>
     </row>
     <row r="77" spans="1:12">
-      <c r="A77" s="25"/>
+      <c r="A77" s="16"/>
       <c r="B77" s="3">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -11082,7 +11511,7 @@
       <c r="L77" s="9"/>
     </row>
     <row r="78" spans="1:12">
-      <c r="A78" s="25"/>
+      <c r="A78" s="16"/>
       <c r="B78" s="3">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -11099,7 +11528,7 @@
       <c r="L78" s="9"/>
     </row>
     <row r="79" spans="1:12">
-      <c r="A79" s="25"/>
+      <c r="A79" s="16"/>
       <c r="B79" s="3">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -11120,7 +11549,7 @@
       </c>
     </row>
     <row r="80" spans="1:12">
-      <c r="A80" s="25"/>
+      <c r="A80" s="16"/>
       <c r="B80" s="3">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -11141,7 +11570,7 @@
       </c>
     </row>
     <row r="81" spans="1:12">
-      <c r="A81" s="25"/>
+      <c r="A81" s="16"/>
       <c r="B81" s="3">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -11162,7 +11591,17 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="17">
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="I16:I19"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="I30:I33"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="E4:J4"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="J36:J37"/>
     <mergeCell ref="A50:A81"/>
     <mergeCell ref="K48:L48"/>
     <mergeCell ref="C47:J47"/>
@@ -11170,14 +11609,6 @@
     <mergeCell ref="E48:F48"/>
     <mergeCell ref="G48:H48"/>
     <mergeCell ref="I48:J48"/>
-    <mergeCell ref="G38:G39"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:I4"/>
-    <mergeCell ref="I16:I19"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="I30:I33"/>
-    <mergeCell ref="G26:G27"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11292,12 +11723,16 @@
         <v>46036</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="15" spans="2:3">
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
+      <c r="B15" s="11">
+        <v>46101</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>414</v>
+      </c>
     </row>
     <row r="16" spans="2:3">
       <c r="B16" s="11"/>
@@ -11361,6 +11796,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C98D15B0064474782E8EDBA35A51CC2" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="84bc66ae19ca557e54d7014d86ef62c3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6946600b-d432-4ec1-a6de-e6a1f3354bfd" xmlns:ns3="43135f08-7c27-4a7c-bc6d-152a25501e39" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f294aa8e50c0a16a8ee0b06cd98abedc" ns2:_="" ns3:_="">
     <xsd:import namespace="6946600b-d432-4ec1-a6de-e6a1f3354bfd"/>
@@ -11567,15 +12011,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58D7A352-4E74-4D3B-B371-7F84A478DD81}">
   <ds:schemaRefs>
@@ -11588,6 +12023,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{993051E6-CE55-49FB-9812-9A2B302725FA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A02F2913-AEC8-45FD-9F40-2703FA5F6AAD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11604,12 +12047,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{993051E6-CE55-49FB-9812-9A2B302725FA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>